--- a/Kicad/H10 Pi Pico/H10 Pico Info.xlsx
+++ b/Kicad/H10 Pi Pico/H10 Pico Info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Heathkit H10 Paper Tape Punch-Reader\H10-Paper-Tape-Reader-Punch\Kicad\H10 Pi Pico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D17CB7BD-1D2A-4150-AAE5-4716D2CFDADF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{761E7E89-6C33-4A27-933F-2501FA202F87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4920" yWindow="756" windowWidth="20352" windowHeight="14568" firstSheet="3" activeTab="7" xr2:uid="{935E9EDB-3516-4202-A772-0300CBF99495}"/>
+    <workbookView xWindow="1536" yWindow="1536" windowWidth="22164" windowHeight="12660" firstSheet="3" activeTab="5" xr2:uid="{935E9EDB-3516-4202-A772-0300CBF99495}"/>
   </bookViews>
   <sheets>
     <sheet name="RedBoard T" sheetId="1" r:id="rId1"/>
@@ -16373,274 +16373,274 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
-        <v>869</v>
+        <v>885</v>
       </c>
       <c r="C15" t="s">
+        <v>830</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>858</v>
+      </c>
+      <c r="F15" t="s">
         <v>832</v>
       </c>
-      <c r="E15" s="7" t="s">
-        <v>853</v>
-      </c>
-      <c r="F15" t="s">
-        <v>830</v>
-      </c>
       <c r="G15" t="s">
-        <v>870</v>
+        <v>886</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
-        <v>871</v>
+        <v>887</v>
       </c>
       <c r="C16" t="s">
+        <v>830</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>858</v>
+      </c>
+      <c r="F16" t="s">
         <v>832</v>
       </c>
-      <c r="E16" s="7" t="s">
-        <v>853</v>
-      </c>
-      <c r="F16" t="s">
-        <v>830</v>
-      </c>
       <c r="G16" t="s">
-        <v>872</v>
+        <v>888</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
-        <v>873</v>
+        <v>889</v>
       </c>
       <c r="C17" t="s">
+        <v>830</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>858</v>
+      </c>
+      <c r="F17" t="s">
         <v>832</v>
       </c>
-      <c r="E17" s="7" t="s">
-        <v>853</v>
-      </c>
-      <c r="F17" t="s">
-        <v>830</v>
-      </c>
       <c r="G17" t="s">
-        <v>874</v>
+        <v>890</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
-        <v>875</v>
+        <v>891</v>
       </c>
       <c r="C18" t="s">
+        <v>830</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>858</v>
+      </c>
+      <c r="F18" t="s">
         <v>832</v>
       </c>
-      <c r="E18" s="7" t="s">
-        <v>853</v>
-      </c>
-      <c r="F18" t="s">
-        <v>830</v>
-      </c>
       <c r="G18" t="s">
-        <v>876</v>
+        <v>892</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
-        <v>877</v>
+        <v>893</v>
       </c>
       <c r="C19" t="s">
+        <v>830</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>858</v>
+      </c>
+      <c r="F19" t="s">
         <v>832</v>
       </c>
-      <c r="E19" s="7" t="s">
-        <v>853</v>
-      </c>
-      <c r="F19" t="s">
-        <v>830</v>
-      </c>
       <c r="G19" t="s">
-        <v>878</v>
+        <v>894</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
-        <v>879</v>
+        <v>895</v>
       </c>
       <c r="C20" t="s">
+        <v>830</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>858</v>
+      </c>
+      <c r="F20" t="s">
         <v>832</v>
       </c>
-      <c r="E20" s="7" t="s">
-        <v>853</v>
-      </c>
-      <c r="F20" t="s">
-        <v>830</v>
-      </c>
       <c r="G20" t="s">
-        <v>880</v>
+        <v>896</v>
       </c>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
-        <v>881</v>
+        <v>897</v>
       </c>
       <c r="C21" t="s">
+        <v>830</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>858</v>
+      </c>
+      <c r="F21" t="s">
         <v>832</v>
       </c>
-      <c r="E21" s="7" t="s">
-        <v>853</v>
-      </c>
-      <c r="F21" t="s">
-        <v>830</v>
-      </c>
       <c r="G21" t="s">
-        <v>882</v>
+        <v>898</v>
       </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
-        <v>883</v>
+        <v>899</v>
       </c>
       <c r="C22" t="s">
+        <v>830</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>858</v>
+      </c>
+      <c r="F22" t="s">
         <v>832</v>
       </c>
-      <c r="E22" s="7" t="s">
-        <v>853</v>
-      </c>
-      <c r="F22" t="s">
-        <v>830</v>
-      </c>
       <c r="G22" t="s">
-        <v>884</v>
+        <v>900</v>
       </c>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
-        <v>885</v>
+        <v>869</v>
       </c>
       <c r="C24" t="s">
+        <v>832</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>853</v>
+      </c>
+      <c r="F24" t="s">
         <v>830</v>
       </c>
-      <c r="E24" s="7" t="s">
-        <v>858</v>
-      </c>
-      <c r="F24" t="s">
-        <v>832</v>
-      </c>
       <c r="G24" t="s">
-        <v>886</v>
+        <v>870</v>
       </c>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
-        <v>887</v>
+        <v>871</v>
       </c>
       <c r="C25" t="s">
+        <v>832</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>853</v>
+      </c>
+      <c r="F25" t="s">
         <v>830</v>
       </c>
-      <c r="E25" s="7" t="s">
-        <v>858</v>
-      </c>
-      <c r="F25" t="s">
-        <v>832</v>
-      </c>
       <c r="G25" t="s">
-        <v>888</v>
+        <v>872</v>
       </c>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
-        <v>889</v>
+        <v>873</v>
       </c>
       <c r="C26" t="s">
+        <v>832</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>853</v>
+      </c>
+      <c r="F26" t="s">
         <v>830</v>
       </c>
-      <c r="E26" s="7" t="s">
-        <v>858</v>
-      </c>
-      <c r="F26" t="s">
-        <v>832</v>
-      </c>
       <c r="G26" t="s">
-        <v>890</v>
+        <v>874</v>
       </c>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
-        <v>891</v>
+        <v>875</v>
       </c>
       <c r="C27" t="s">
+        <v>832</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>853</v>
+      </c>
+      <c r="F27" t="s">
         <v>830</v>
       </c>
-      <c r="E27" s="7" t="s">
-        <v>858</v>
-      </c>
-      <c r="F27" t="s">
-        <v>832</v>
-      </c>
       <c r="G27" t="s">
-        <v>892</v>
+        <v>876</v>
       </c>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
-        <v>893</v>
+        <v>877</v>
       </c>
       <c r="C28" t="s">
+        <v>832</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>853</v>
+      </c>
+      <c r="F28" t="s">
         <v>830</v>
       </c>
-      <c r="E28" s="7" t="s">
-        <v>858</v>
-      </c>
-      <c r="F28" t="s">
-        <v>832</v>
-      </c>
       <c r="G28" t="s">
-        <v>894</v>
+        <v>878</v>
       </c>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
-        <v>895</v>
+        <v>879</v>
       </c>
       <c r="C29" t="s">
+        <v>832</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>853</v>
+      </c>
+      <c r="F29" t="s">
         <v>830</v>
       </c>
-      <c r="E29" s="7" t="s">
-        <v>858</v>
-      </c>
-      <c r="F29" t="s">
-        <v>832</v>
-      </c>
       <c r="G29" t="s">
-        <v>896</v>
+        <v>880</v>
       </c>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
-        <v>897</v>
+        <v>881</v>
       </c>
       <c r="C30" t="s">
+        <v>832</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>853</v>
+      </c>
+      <c r="F30" t="s">
         <v>830</v>
       </c>
-      <c r="E30" s="7" t="s">
-        <v>858</v>
-      </c>
-      <c r="F30" t="s">
-        <v>832</v>
-      </c>
       <c r="G30" t="s">
-        <v>898</v>
+        <v>882</v>
       </c>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
-        <v>899</v>
+        <v>883</v>
       </c>
       <c r="C31" t="s">
+        <v>832</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>853</v>
+      </c>
+      <c r="F31" t="s">
         <v>830</v>
       </c>
-      <c r="E31" s="7" t="s">
-        <v>858</v>
-      </c>
-      <c r="F31" t="s">
-        <v>832</v>
-      </c>
       <c r="G31" t="s">
-        <v>900</v>
+        <v>884</v>
       </c>
     </row>
   </sheetData>
